--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -53,15 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
   </si>
   <si>
     <t>В8330НТ</t>
@@ -113,8 +104,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -200,11 +192,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -212,9 +205,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,20 +561,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46149</v>
       </c>
       <c r="B2">
         <v>1148</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -599,7 +592,7 @@
         <v>180</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -609,20 +602,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46154</v>
       </c>
       <c r="B3">
         <v>1148</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>73.26300000000001</v>
@@ -640,7 +633,7 @@
         <v>131.14</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -650,20 +643,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
+      <c r="A4" s="2">
+        <v>46155</v>
       </c>
       <c r="B4">
         <v>1148</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>24.179</v>
@@ -681,7 +674,7 @@
         <v>43.28</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -691,80 +684,80 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6">
         <v>197.442</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="6">
         <v>3</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="6">
         <v>1.7651</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="6">
         <v>348.5</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="6">
         <v>354.42</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <v>5.92</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="7">
+      <c r="A10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="8">
         <v>197.442</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>3</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8">
         <v>348.5</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>354.42</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>5.92</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
@@ -137,7 +137,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,12 +147,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -203,17 +197,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="21">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,16 +46,10 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В8330НТ</t>
@@ -68,21 +59,6 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:20:00</t>
-  </si>
-  <si>
-    <t>06:11:00</t>
-  </si>
-  <si>
-    <t>3232105513 3232105513</t>
-  </si>
-  <si>
-    <t>3232523940 3232523940</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС</t>
@@ -502,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -511,17 +487,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,175 +528,183 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
       </c>
       <c r="F2">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H2">
+        <v>132.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J2">
+        <v>135.2</v>
+      </c>
+      <c r="K2">
+        <v>117388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>90</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H3">
+        <v>144.9</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J3">
+        <v>147.6</v>
+      </c>
+      <c r="K3">
+        <v>117776</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>69.89</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="H4">
+        <v>109.73</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J4">
+        <v>111.82</v>
+      </c>
+      <c r="K4">
+        <v>118085</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H2">
-        <v>1.72</v>
-      </c>
-      <c r="I2" s="1">
-        <v>137.6</v>
-      </c>
-      <c r="J2">
-        <v>1.75</v>
-      </c>
-      <c r="K2" s="1">
-        <v>140</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M2">
-        <v>116488</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3">
-        <v>110</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3">
-        <v>1.68</v>
-      </c>
-      <c r="I3" s="1">
-        <v>184.8</v>
-      </c>
-      <c r="J3">
-        <v>1.71</v>
-      </c>
-      <c r="K3" s="1">
-        <v>188.1</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="B9" s="7">
+        <v>239.89</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.615</v>
+      </c>
+      <c r="E9" s="7">
+        <v>387.43</v>
+      </c>
+      <c r="F9" s="7">
+        <v>394.62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="M3">
-        <v>116975</v>
-      </c>
-      <c r="N3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="7">
-        <v>190</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.6968</v>
-      </c>
-      <c r="E8" s="7">
-        <v>322.4</v>
-      </c>
-      <c r="F8" s="7">
-        <v>328.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="10">
-        <v>190</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>322.4</v>
-      </c>
-      <c r="F9" s="10">
-        <v>328.1</v>
+      <c r="B10" s="10">
+        <v>239.89</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>387.43</v>
+      </c>
+      <c r="F10" s="10">
+        <v>394.62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -59,6 +65,15 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>06:12</t>
+  </si>
+  <si>
+    <t>06:32</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС</t>
@@ -478,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -491,10 +506,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -528,22 +545,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46177</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>80</v>
@@ -560,25 +583,31 @@
       <c r="J2">
         <v>135.2</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
         <v>117388</v>
       </c>
+      <c r="M2">
+        <v>214596</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46183</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3">
         <v>90</v>
@@ -595,25 +624,31 @@
       <c r="J3">
         <v>147.6</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3">
         <v>117776</v>
       </c>
+      <c r="M3">
+        <v>217018</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46188</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>69.89</v>
@@ -630,13 +665,19 @@
       <c r="J4">
         <v>111.82</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4">
         <v>118085</v>
       </c>
+      <c r="M4">
+        <v>219154</v>
+      </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -644,18 +685,18 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>7</v>
@@ -664,9 +705,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="7">
         <v>239.89</v>
@@ -684,9 +725,9 @@
         <v>394.62</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B10" s="10">
         <v>239.89</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС/ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В8330НТ</t>
@@ -70,13 +67,7 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>06:21:00</t>
-  </si>
-  <si>
-    <t>3233872589 3233872589</t>
+    <t>06:21</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 4 - УЧИЛИЩЕН АВТОБУС</t>
@@ -496,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,17 +496,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,57 +545,51 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46199</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
       </c>
       <c r="F2">
         <v>60</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="H2">
+        <v>88.8</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J2">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>118380</v>
+      </c>
+      <c r="M2">
+        <v>224125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="H2">
-        <v>1.48</v>
-      </c>
-      <c r="I2" s="1">
-        <v>88.8</v>
-      </c>
-      <c r="J2">
-        <v>1.51</v>
-      </c>
-      <c r="K2" s="1">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>118380</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -613,29 +597,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>60</v>
@@ -653,9 +637,9 @@
         <v>90.59999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" s="10">
         <v>60</v>
